--- a/artfynd/A 53409-2022 artfynd.xlsx
+++ b/artfynd/A 53409-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123712974</v>
+        <v>123712976</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514797</v>
+        <v>514847</v>
       </c>
       <c r="R2" t="n">
-        <v>6731006</v>
+        <v>6730989</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
+          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123712976</v>
+        <v>123712974</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514847</v>
+        <v>514797</v>
       </c>
       <c r="R3" t="n">
-        <v>6730989</v>
+        <v>6731006</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
+          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,7 +938,7 @@
         <v>123712973</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53409-2022 artfynd.xlsx
+++ b/artfynd/A 53409-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123712976</v>
+        <v>123712973</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514847</v>
+        <v>514807</v>
       </c>
       <c r="R2" t="n">
-        <v>6730989</v>
+        <v>6731015</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
+          <t>En tredje bild på Knärot bara någon meter från Bergkvist Siljans nyligen gjorda avverkning.(73, 74, 75). Uppskattat antal, går inte räkna.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123712974</v>
+        <v>123712976</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514797</v>
+        <v>514847</v>
       </c>
       <c r="R3" t="n">
-        <v>6731006</v>
+        <v>6730989</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
+          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123712973</v>
+        <v>123712974</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -983,14 +983,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514807</v>
+        <v>514797</v>
       </c>
       <c r="R4" t="n">
-        <v>6731015</v>
+        <v>6731006</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En tredje bild på Knärot bara någon meter från Bergkvist Siljans nyligen gjorda avverkning.(73, 74, 75). Uppskattat antal, går inte räkna.</t>
+          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 53409-2022 artfynd.xlsx
+++ b/artfynd/A 53409-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123712973</v>
+        <v>123712974</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,14 +723,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514807</v>
+        <v>514797</v>
       </c>
       <c r="R2" t="n">
-        <v>6731015</v>
+        <v>6731006</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En tredje bild på Knärot bara någon meter från Bergkvist Siljans nyligen gjorda avverkning.(73, 74, 75). Uppskattat antal, går inte räkna.</t>
+          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,7 +805,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123712974</v>
+        <v>123712976</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,14 +853,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågen, Dlr</t>
+          <t>sågen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514797</v>
+        <v>514847</v>
       </c>
       <c r="R3" t="n">
-        <v>6731006</v>
+        <v>6730989</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
+          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +935,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123712976</v>
+        <v>123712973</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -970,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514847</v>
+        <v>514807</v>
       </c>
       <c r="R4" t="n">
-        <v>6730989</v>
+        <v>6731015</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
+          <t>En tredje bild på Knärot bara någon meter från Bergkvist Siljans nyligen gjorda avverkning.(73, 74, 75). Uppskattat antal, går inte räkna.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 53409-2022 artfynd.xlsx
+++ b/artfynd/A 53409-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123712974</v>
+        <v>123712972</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514797</v>
+        <v>514858</v>
       </c>
       <c r="R2" t="n">
-        <v>6731006</v>
+        <v>6731044</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
+          <t>En bild på Knärot från en giltig avverkningsanmälan mellan en ännu ej giltig anmälan och en avverkad anmälan. I alla tre, samt i ett område som Mellanskog har gallrat) finns Knärot. Inget område hade någon Hänsynsmarkering för Knärot. Uppskattat antal. En miljöbild tagen i samma anmälan (76, 77)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123712976</v>
+        <v>123712973</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +830,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -857,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514847</v>
+        <v>514807</v>
       </c>
       <c r="R3" t="n">
-        <v>6730989</v>
+        <v>6731015</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
+          <t>En tredje bild på Knärot bara någon meter från Bergkvist Siljans nyligen gjorda avverkning.(73, 74, 75). Uppskattat antal, går inte räkna.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123712973</v>
+        <v>123712974</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,14 +968,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>sågen, Dlr</t>
+          <t>Sågen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514807</v>
+        <v>514797</v>
       </c>
       <c r="R4" t="n">
-        <v>6731015</v>
+        <v>6731006</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1022,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En tredje bild på Knärot bara någon meter från Bergkvist Siljans nyligen gjorda avverkning.(73, 74, 75). Uppskattat antal, går inte räkna.</t>
+          <t>Ytterligare en bild från Bergkvist Siljans avverkning nyligen.  (72.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,6 +1047,238 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123712976</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514847</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6730989</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Från en avverkning som Bergkvist Siljan nyligen har gjort. Bilderna på den nerrisade bäcken hade jag tagit när jag kom fram till två gulgröna Knärot. Bäcken har sitt utlopp i Årbosjön, som är en källsjö! Hur många knärot som fanns där körvägarna går är omöjligt att säga.   64, (65-68 o 69).</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123958246</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514844</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6730969</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53409-2022 artfynd.xlsx
+++ b/artfynd/A 53409-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712974</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123712976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,8 +1304,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123958246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>